--- a/НИР_ЭДО_ПОЛНЫЙ_АРХИВ/05_Судебная_практика/Сравнение_судебных_практик.xlsx
+++ b/НИР_ЭДО_ПОЛНЫЙ_АРХИВ/05_Судебная_практика/Сравнение_судебных_практик.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -571,6 +571,18 @@
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Ст. 22.1(3) ТК — статутный запрет носителя. Среди 14 карточек нет судебного подтверждения, что электронный журнал ОТ всегда недопустим.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Как проверить</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>В таблице «Все_14_практик» колонки «Ссылка 1» и «Ссылка 2» кликабельны: это текст дела или официальная норма. Лист «Источники» дублирует полный список URL.</t>
         </is>
       </c>
     </row>
@@ -589,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -600,6 +612,7 @@
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -645,7 +658,12 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Ссылка</t>
+          <t>Ссылка 1 (проверить)</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Ссылка 2 (проверить)</t>
         </is>
       </c>
     </row>
@@ -695,6 +713,11 @@
           <t>https://www.bundesgerichtshof.de/SharedDocs/Entscheidungen/DE/Zivilsenate/VIII_ZS/2023/VIII_ZR_155-23.pdf?__blob=publicationFile&amp;v=1</t>
         </is>
       </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>https://rewis.io/urteile/urteil/wfg-27-11-2024-viii-zr-15523/</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="92" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -742,6 +765,7 @@
           <t>https://www.bundesarbeitsgericht.de/entscheidung/1-abr-104-09/</t>
         </is>
       </c>
+      <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="92" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -789,6 +813,11 @@
           <t>https://zakony-by.com/hozyajstvennyj_protsessualnyj_kodeks_rb/84.htm</t>
         </is>
       </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>https://bii.by/docs/ispolzovanie-dokumentov-v-elektronnom-vide-v-dogovornykh-otnosheniyakh-sudebnaya-praktika-358365</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="92" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -836,6 +865,11 @@
           <t>https://www.mintrud.gov.by/uploads/files/MTiSZ-175-po-sost.-na-02.09.2024.pdf</t>
         </is>
       </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>https://zakony-by.com/hozyajstvennyj_protsessualnyj_kodeks_rb/84.htm</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="92" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -883,6 +917,11 @@
           <t>https://www.prlegal.rs/filing-a-complaint-via-email-yes-it-is-possible/</t>
         </is>
       </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prlegal.rs/electronic-signing-of-documents-in-serbia-novelties-in-signing-of-financial-statements-for-business-registers-agency/</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="92" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -930,6 +969,11 @@
           <t>https://www.lexology.com/library/detail.aspx?g=123a20c5-c0a7-425d-8c37-c9892c70dc93</t>
         </is>
       </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prlegal.rs/electronic-signing-of-documents-in-serbia-novelties-in-signing-of-financial-statements-for-business-registers-agency/</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="92" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -977,6 +1021,11 @@
           <t>https://www.boe.es/eli/es/l/2020/11/11/6</t>
         </is>
       </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>https://www.legaltoday.com/practica-juridica/derecho-penal/valor-probatorio-de-los-pantallazos-de-conversaciones-de-whatsapp-o-sus-transcripciones-sts-116-2025-de-13-de-febrero-2025-09-29/</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="92" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1024,6 +1073,11 @@
           <t>https://www.boe.es/buscar/act.php?id=BOE-A-1995-24292</t>
         </is>
       </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>https://lex.ahk.es/actualidad-juridica/puede-la-empresa-emplear-la-firma-electronica-en-el-ambito-laboral</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="92" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1071,6 +1125,11 @@
           <t>https://www.bailii.org/ie/cases/IEHC/2010/H47.html</t>
         </is>
       </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>https://www.irishstatutebook.ie/eli/2000/act/27/section/9/enacted/en/html</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="92" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1118,6 +1177,7 @@
           <t>https://www.bailii.org/ie/cases/IEHC/2024/2024IEHC167.html</t>
         </is>
       </c>
+      <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="92" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1165,6 +1225,11 @@
           <t>https://www.legalis.net/jurisprudences/cour-de-cassation-civile-ch-civile-3-arret-du-5-mars-2026/</t>
         </is>
       </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.doctrine.fr/d/CASS/2026/CASSP5F27671B4851EF0B45AF</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="92" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1212,6 +1277,11 @@
           <t>https://ogletree.fr/publications/od-flash-resiliation-judiciaire-du-contrat-de-travail-et-accident-du-travail-charge-de-la-preuve-en-cas-de-manquement-de-lemployeur-aux-regles-de-prevention-et-de-securite/</t>
         </is>
       </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/av/fr/avocats/eclairages/2023/01/valeur-juridique-de-la-signature-numerisee.html</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="92" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1259,6 +1329,11 @@
           <t>https://new.kenyalaw.org/akn/ke/judgment/keelc/2025/392/eng@2025-02-06</t>
         </is>
       </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>https://new.kenyalaw.org/akn/ke/doc/newsletter/2025-05-12/kenya-law-weekly-issue-04224-25/eng@2025-05-12</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="92" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1304,25 +1379,42 @@
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>https://sheriahub.com/cases/ke/caselaw/bigot-flowers-kenya-ltd-v-cheboswony-employment-and-labour-relations-appeal-10of-2018-2022-keelrc-3772-klr-10may-2022-judgment.pdf</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>https://new.kenyalaw.org/akn/ke/act/2007/15</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1438,12 +1530,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="85" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1462,6 +1555,11 @@
           <t>Семь стран (по карточкам)</t>
         </is>
       </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Ссылка для проверки</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="72" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -1479,6 +1577,11 @@
           <t>Судебного запрета нет. BY — прямое разрешение нормой. RS — бумажный Form 6. DE/ES/IE/FR — содержание обучения</t>
         </is>
       </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_34683/</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -1496,6 +1599,11 @@
           <t>FR 2026: презумпция только у QES. ES: презумпция квалифицированного сервиса. KE: вход через 106B</t>
         </is>
       </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/buscar/act.php?id=BOE-A-2000-323#a326</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1513,6 +1621,11 @@
           <t>Франция прямо: скан ≠ электронная подпись (1367), но не всегда «нет подписи»</t>
         </is>
       </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/av/fr/avocats/eclairages/2023/01/valeur-juridique-de-la-signature-numerisee.html</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1530,6 +1643,11 @@
           <t>BY ст. 84 ХПК прямо включает эл. документы. KE без 106B снимает даже «живой» файл</t>
         </is>
       </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_181602/</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1547,8 +1665,20 @@
           <t>BY п. 35 — положительная модель журнала. FR/ES — презумпция и антискан. DE Zugang — для уведомлений, не обязательно для внутренней отметки</t>
         </is>
       </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mintrud.gov.by/uploads/files/MTiSZ-175-po-sost.-na-02.09.2024.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
